--- a/Result/profitability/9927.xlsx
+++ b/Result/profitability/9927.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.97</v>
+        <v>0.97375</v>
       </c>
       <c r="N2" t="n">
-        <v>10.8475</v>
+        <v>10.2425</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8099999999999999</v>
+        <v>0.78125</v>
       </c>
       <c r="N3" t="n">
-        <v>9.935</v>
+        <v>9.536249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.63875</v>
+        <v>0.63375</v>
       </c>
       <c r="N4" t="n">
-        <v>7.607500000000001</v>
+        <v>7.10375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>0.33625</v>
+        <v>0.47125</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9075</v>
+        <v>3.33625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.41625</v>
+        <v>0.38875</v>
       </c>
       <c r="N6" t="n">
-        <v>4.262499999999999</v>
+        <v>3.94625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3625</v>
+        <v>0.32375</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5975</v>
+        <v>4.095</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45</v>
+        <v>0.45375</v>
       </c>
       <c r="N8" t="n">
-        <v>5.52</v>
+        <v>5.46875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.48375</v>
       </c>
       <c r="N9" t="n">
-        <v>6.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.59</v>
       </c>
       <c r="N10" t="n">
-        <v>7.9925</v>
+        <v>7.992500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.5675</v>
       </c>
       <c r="N11" t="n">
-        <v>7.126250000000001</v>
+        <v>7.12625</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2574</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2353</v>
+      </c>
+      <c r="E75" t="n">
+        <v>222</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>165</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.40%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>170</v>
+      </c>
+      <c r="K75" t="n">
+        <v>138</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.55875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.0299999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02678571428571419</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04545454545454553</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>15.42857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3467374810318665</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
